--- a/muban_clean/zhubaojiao.xlsx
+++ b/muban_clean/zhubaojiao.xlsx
@@ -2735,20 +2735,27 @@
     <font>
       <vertAlign val="superscript"/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="新宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <vertAlign val="superscript"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="新宋体"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="11"/>
+      <name val="新宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2761,13 +2768,6 @@
     <font>
       <vertAlign val="superscript"/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <vertAlign val="superscript"/>
-      <sz val="11"/>
-      <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
